--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/bio-bio.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/bio-bio.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7352.99</v>
+        <v>7392.11</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8054.82</v>
+        <v>8044.33</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8291.67</v>
+        <v>8341.08</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9428.639999999999</v>
+        <v>9403.809999999999</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>16646.57</v>
+        <v>16687.89</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>56017.28</v>
+        <v>55872.01</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8816.110000000001</v>
+        <v>8612.389999999999</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>766143.0699999999</v>
+        <v>750328.3100000001</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>19618.5</v>
+        <v>19620.53</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7335.96</v>
+        <v>7267.5</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>14143.64</v>
+        <v>14346.73</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>20172.12</v>
+        <v>20314.86</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>17290.32</v>
+        <v>17412.68</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/bio-bio.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057417-41801-CM25</t>
+          <t>2078-69-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7392.11</v>
+        <v>30132.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2760-96-CM25</t>
+          <t>1057417-41801-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SECAPPS TECHNOLOGIES SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.660.154-3</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8044.33</v>
+        <v>7392.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057420-102-CM26</t>
+          <t>2760-96-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SECAPPS TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>77.660.154-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8341.08</v>
+        <v>8044.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3734-150-CM26</t>
+          <t>1057420-102-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9403.809999999999</v>
+        <v>8341.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4079-68-CM26</t>
+          <t>3734-150-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>16687.89</v>
+        <v>9403.809999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2078-723-CM26</t>
+          <t>4079-68-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>ZECOVERY LTDA   -    EXEC</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>55872.01</v>
+        <v>16687.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057415-2855-CM26</t>
+          <t>2078-723-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ANTICA S.A.</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.707.140-k</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8612.389999999999</v>
+        <v>55872.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1057414-238-CM26</t>
+          <t>1057415-2855-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>ANTICA S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.707.140-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>750328.3100000001</v>
+        <v>8612.389999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1305504-68-CM26</t>
+          <t>1057414-238-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.046.871-1</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>19620.53</v>
+        <v>750328.3100000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2664-398-CM26</t>
+          <t>1305504-68-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.150.102-7</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.046.871-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7267.5</v>
+        <v>19620.53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1057415-2966-CM26</t>
+          <t>2664-398-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>69.150.102-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>Dirección de Salud Municipal</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>VICTORIA SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>14346.73</v>
+        <v>7267.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057421-460-CM26</t>
+          <t>1057415-2966-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.607.306-0</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>20314.86</v>
+        <v>14346.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057421-461-CM26</t>
+          <t>1057421-460-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,6 +1301,67 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
+        <v>20314.86</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1057421-461-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.607.306-0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
         <v>17412.68</v>
       </c>
     </row>
